--- a/output/pdf_financials_xlsx/SONA.xlsx
+++ b/output/pdf_financials_xlsx/SONA.xlsx
@@ -895,13 +895,13 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.013976</v>
+        <v>0.72</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="29">
@@ -911,13 +911,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.499675</v>
+        <v>-2.079675</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.689981</v>
+        <v>-1.983957</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.250345</v>
+        <v>-2.530345</v>
       </c>
     </row>
     <row r="30">
@@ -4662,17 +4662,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>-0.42</v>
+        <v>0.42</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>-0.72</v>
+        <v>0.72</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.72</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="64">

--- a/output/pdf_financials_xlsx/SONA.xlsx
+++ b/output/pdf_financials_xlsx/SONA.xlsx
@@ -1480,13 +1480,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.900809</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.647303</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.906931</v>
       </c>
     </row>
     <row r="65">
